--- a/dhe_dashboard_v2/data/Bellis.xlsx
+++ b/dhe_dashboard_v2/data/Bellis.xlsx
@@ -1909,7 +1909,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tablo1" displayName="Tablo1" ref="B7:K169" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="B7:K169"/>
+  <autoFilter ref="B7:K169">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Kaya/Abant Su - Bolu"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="B8:J168">
     <sortCondition ref="D68"/>
   </sortState>
@@ -2350,7 +2356,7 @@
       </c>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>1</v>
       </c>
@@ -2384,7 +2390,7 @@
       </c>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>2</v>
       </c>
@@ -2418,7 +2424,7 @@
       </c>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
         <v>3</v>
       </c>
@@ -2454,7 +2460,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
         <v>4</v>
       </c>
@@ -2488,7 +2494,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
         <v>5</v>
       </c>
@@ -2522,7 +2528,7 @@
       </c>
       <c r="L12" s="20"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27">
         <v>6</v>
       </c>
@@ -2556,7 +2562,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
         <v>7</v>
       </c>
@@ -2592,7 +2598,7 @@
       </c>
       <c r="L14" s="20"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
         <v>8</v>
       </c>
@@ -2628,7 +2634,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
         <v>9</v>
       </c>
@@ -2664,7 +2670,7 @@
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
         <v>10</v>
       </c>
@@ -2698,7 +2704,7 @@
       </c>
       <c r="L17" s="20"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
         <v>11</v>
       </c>
@@ -2732,7 +2738,7 @@
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27">
         <v>12</v>
       </c>
@@ -2766,7 +2772,7 @@
       </c>
       <c r="L19" s="20"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="27">
         <v>13</v>
       </c>
@@ -2798,7 +2804,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27">
         <v>14</v>
       </c>
@@ -2834,7 +2840,7 @@
       </c>
       <c r="L21" s="20"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
         <v>15</v>
       </c>
@@ -2868,7 +2874,7 @@
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
         <v>16</v>
       </c>
@@ -2902,7 +2908,7 @@
       </c>
       <c r="L23" s="20"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
         <v>17</v>
       </c>
@@ -2938,7 +2944,7 @@
       </c>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>18</v>
       </c>
@@ -2974,7 +2980,7 @@
       </c>
       <c r="L25" s="20"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
         <v>19</v>
       </c>
@@ -3008,7 +3014,7 @@
       </c>
       <c r="L26" s="19"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>20</v>
       </c>
@@ -3042,7 +3048,7 @@
       </c>
       <c r="L27" s="20"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>21</v>
       </c>
@@ -3076,7 +3082,7 @@
       </c>
       <c r="L28" s="19"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
         <v>22</v>
       </c>
@@ -3110,7 +3116,7 @@
       </c>
       <c r="L29" s="20"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27">
         <v>23</v>
       </c>
@@ -3144,7 +3150,7 @@
       </c>
       <c r="L30" s="19"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="27">
         <v>24</v>
       </c>
@@ -3178,7 +3184,7 @@
       </c>
       <c r="L31" s="19"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27">
         <v>25</v>
       </c>
@@ -3214,7 +3220,7 @@
       </c>
       <c r="L32" s="20"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27">
         <v>26</v>
       </c>
@@ -3250,7 +3256,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="27">
         <v>27</v>
       </c>
@@ -3286,7 +3292,7 @@
       </c>
       <c r="L34" s="19"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="27">
         <v>28</v>
       </c>
@@ -3322,7 +3328,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="27">
         <v>29</v>
       </c>
@@ -3358,7 +3364,7 @@
       </c>
       <c r="L36" s="19"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="27">
         <v>30</v>
       </c>
@@ -3394,7 +3400,7 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="27">
         <v>31</v>
       </c>
@@ -3430,7 +3436,7 @@
       </c>
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="27">
         <v>32</v>
       </c>
@@ -3464,7 +3470,7 @@
       </c>
       <c r="L39" s="19"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
         <v>33</v>
       </c>
@@ -3498,7 +3504,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="27">
         <v>34</v>
       </c>
@@ -3532,7 +3538,7 @@
       </c>
       <c r="L41" s="19"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="27">
         <v>35</v>
       </c>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="27">
         <v>36</v>
       </c>
@@ -3600,7 +3606,7 @@
       </c>
       <c r="L43" s="19"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="27">
         <v>37</v>
       </c>
@@ -3634,7 +3640,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27">
         <v>38</v>
       </c>
@@ -3668,7 +3674,7 @@
       </c>
       <c r="L45" s="19"/>
     </row>
-    <row r="46" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="27">
         <v>39</v>
       </c>
@@ -3702,7 +3708,7 @@
       </c>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="27">
         <v>40</v>
       </c>
@@ -3738,7 +3744,7 @@
       </c>
       <c r="L47" s="19"/>
     </row>
-    <row r="48" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="27">
         <v>41</v>
       </c>
@@ -3774,7 +3780,7 @@
       </c>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="27">
         <v>42</v>
       </c>
@@ -3810,7 +3816,7 @@
       </c>
       <c r="L49" s="19"/>
     </row>
-    <row r="50" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="27">
         <v>43</v>
       </c>
@@ -3846,7 +3852,7 @@
       </c>
       <c r="L50" s="20"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="27">
         <v>44</v>
       </c>
@@ -3880,7 +3886,7 @@
       </c>
       <c r="L51" s="19"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="27">
         <v>45</v>
       </c>
@@ -3916,7 +3922,7 @@
       </c>
       <c r="L52" s="20"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="27">
         <v>46</v>
       </c>
@@ -3950,7 +3956,7 @@
       </c>
       <c r="L53" s="19"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="27">
         <v>47</v>
       </c>
@@ -3984,7 +3990,7 @@
       </c>
       <c r="L54" s="20"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="27">
         <v>48</v>
       </c>
@@ -4018,7 +4024,7 @@
       </c>
       <c r="L55" s="19"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="27">
         <v>49</v>
       </c>
@@ -4052,7 +4058,7 @@
       </c>
       <c r="L56" s="20"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="27">
         <v>50</v>
       </c>
@@ -4086,7 +4092,7 @@
       </c>
       <c r="L57" s="19"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="27">
         <v>51</v>
       </c>
@@ -4120,7 +4126,7 @@
       </c>
       <c r="L58" s="20"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="27">
         <v>52</v>
       </c>
@@ -4154,7 +4160,7 @@
       </c>
       <c r="L59" s="19"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="27">
         <v>53</v>
       </c>
@@ -4188,7 +4194,7 @@
       </c>
       <c r="L60" s="20"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="27">
         <v>54</v>
       </c>
@@ -4222,7 +4228,7 @@
       </c>
       <c r="L61" s="19"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="27">
         <v>55</v>
       </c>
@@ -4258,7 +4264,7 @@
       </c>
       <c r="L62" s="20"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="27">
         <v>56</v>
       </c>
@@ -4294,7 +4300,7 @@
       </c>
       <c r="L63" s="19"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="27">
         <v>57</v>
       </c>
@@ -4330,7 +4336,7 @@
       </c>
       <c r="L64" s="20"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="27">
         <v>58</v>
       </c>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="L65" s="19"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="27">
         <v>59</v>
       </c>
@@ -4400,7 +4406,7 @@
       </c>
       <c r="L66" s="20"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="27">
         <v>60</v>
       </c>
@@ -4436,7 +4442,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="27">
         <v>61</v>
       </c>
@@ -4474,7 +4480,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="27">
         <v>62</v>
       </c>
@@ -4510,7 +4516,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="27">
         <v>63</v>
       </c>
@@ -4548,7 +4554,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="27">
         <v>64</v>
       </c>
@@ -4584,7 +4590,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="27">
         <v>65</v>
       </c>
@@ -4620,7 +4626,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="27">
         <v>66</v>
       </c>
@@ -4656,7 +4662,7 @@
       </c>
       <c r="L73" s="20"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="27">
         <v>67</v>
       </c>
@@ -4690,7 +4696,7 @@
       </c>
       <c r="L74" s="19"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="27">
         <v>68</v>
       </c>
@@ -4748,17 +4754,17 @@
         <v>135</v>
       </c>
       <c r="I76" s="16" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="J76" s="16" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="L76" s="19"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="27">
         <v>70</v>
       </c>
@@ -4792,7 +4798,7 @@
       </c>
       <c r="L77" s="20"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="27">
         <v>71</v>
       </c>
@@ -4826,7 +4832,7 @@
       </c>
       <c r="L78" s="20"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="27">
         <v>72</v>
       </c>
@@ -4860,7 +4866,7 @@
       </c>
       <c r="L79" s="20"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="27">
         <v>73</v>
       </c>
@@ -4896,7 +4902,7 @@
       </c>
       <c r="L80" s="19"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="27">
         <v>74</v>
       </c>
@@ -4930,7 +4936,7 @@
       </c>
       <c r="L81" s="20"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="27">
         <v>75</v>
       </c>
@@ -4966,7 +4972,7 @@
       </c>
       <c r="L82" s="20"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="27">
         <v>76</v>
       </c>
@@ -5000,7 +5006,7 @@
       </c>
       <c r="L83" s="19"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="27">
         <v>77</v>
       </c>
@@ -5034,7 +5040,7 @@
       </c>
       <c r="L84" s="20"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="27">
         <v>78</v>
       </c>
@@ -5068,7 +5074,7 @@
       </c>
       <c r="L85" s="19"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="27">
         <v>79</v>
       </c>
@@ -5104,7 +5110,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="27">
         <v>80</v>
       </c>
@@ -5138,7 +5144,7 @@
       </c>
       <c r="L87" s="19"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="27">
         <v>81</v>
       </c>
@@ -5172,7 +5178,7 @@
       </c>
       <c r="L88" s="20"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="27">
         <v>82</v>
       </c>
@@ -5206,7 +5212,7 @@
       </c>
       <c r="L89" s="20"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="27">
         <v>83</v>
       </c>
@@ -5242,7 +5248,7 @@
       </c>
       <c r="L90" s="19"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="27">
         <v>84</v>
       </c>
@@ -5278,7 +5284,7 @@
       </c>
       <c r="L91" s="20"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="27">
         <v>85</v>
       </c>
@@ -5316,7 +5322,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="27">
         <v>86</v>
       </c>
@@ -5350,7 +5356,7 @@
       </c>
       <c r="L93" s="20"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="27">
         <v>87</v>
       </c>
@@ -5384,7 +5390,7 @@
       </c>
       <c r="L94" s="20"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="27">
         <v>88</v>
       </c>
@@ -5418,7 +5424,7 @@
       </c>
       <c r="L95" s="20"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="27">
         <v>89</v>
       </c>
@@ -5452,7 +5458,7 @@
       </c>
       <c r="L96" s="19"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="27">
         <v>90</v>
       </c>
@@ -5488,7 +5494,7 @@
       </c>
       <c r="L97" s="20"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="27">
         <v>91</v>
       </c>
@@ -5524,7 +5530,7 @@
       </c>
       <c r="L98" s="19"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="27">
         <v>92</v>
       </c>
@@ -5560,7 +5566,7 @@
       </c>
       <c r="L99" s="20"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="27">
         <v>93</v>
       </c>
@@ -5596,7 +5602,7 @@
       </c>
       <c r="L100" s="19"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="27">
         <v>94</v>
       </c>
@@ -5632,7 +5638,7 @@
       </c>
       <c r="L101" s="20"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="27">
         <v>95</v>
       </c>
@@ -5666,7 +5672,7 @@
       </c>
       <c r="L102" s="19"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="27">
         <v>96</v>
       </c>
@@ -5700,7 +5706,7 @@
       </c>
       <c r="L103" s="19"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="27">
         <v>97</v>
       </c>
@@ -5736,7 +5742,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="27">
         <v>98</v>
       </c>
@@ -5770,7 +5776,7 @@
       </c>
       <c r="L105" s="19"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="27">
         <v>99</v>
       </c>
@@ -5806,7 +5812,7 @@
       </c>
       <c r="L106" s="20"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="27">
         <v>100</v>
       </c>
@@ -5842,7 +5848,7 @@
       </c>
       <c r="L107" s="19"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="27">
         <v>101</v>
       </c>
@@ -5876,7 +5882,7 @@
       </c>
       <c r="L108" s="20"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="27">
         <v>102</v>
       </c>
@@ -5914,7 +5920,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="27">
         <v>103</v>
       </c>
@@ -5950,7 +5956,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="27">
         <v>104</v>
       </c>
@@ -5986,7 +5992,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="27">
         <v>105</v>
       </c>
@@ -6022,7 +6028,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="27">
         <v>106</v>
       </c>
@@ -6056,7 +6062,7 @@
       </c>
       <c r="L113" s="19"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="27">
         <v>107</v>
       </c>
@@ -6094,7 +6100,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="27">
         <v>108</v>
       </c>
@@ -6130,7 +6136,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="27">
         <v>109</v>
       </c>
@@ -6192,17 +6198,17 @@
         <v>135</v>
       </c>
       <c r="I117" s="16" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="J117" s="16" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="K117" s="24" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="L117" s="19"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="27">
         <v>111</v>
       </c>
@@ -6238,7 +6244,7 @@
       </c>
       <c r="L118" s="20"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="27">
         <v>112</v>
       </c>
@@ -6274,7 +6280,7 @@
       </c>
       <c r="L119" s="19"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="27">
         <v>113</v>
       </c>
@@ -6308,7 +6314,7 @@
       </c>
       <c r="L120" s="20"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="27">
         <v>114</v>
       </c>
@@ -6344,7 +6350,7 @@
       </c>
       <c r="L121" s="19"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="27">
         <v>115</v>
       </c>
@@ -6378,7 +6384,7 @@
       </c>
       <c r="L122" s="20"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="27">
         <v>116</v>
       </c>
@@ -6412,7 +6418,7 @@
       </c>
       <c r="L123" s="19"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="27">
         <v>118</v>
       </c>
@@ -6448,7 +6454,7 @@
       </c>
       <c r="L124" s="20"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="27">
         <v>119</v>
       </c>
@@ -6486,7 +6492,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="27">
         <v>120</v>
       </c>
@@ -6524,7 +6530,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="27">
         <v>121</v>
       </c>
@@ -6562,7 +6568,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="27">
         <v>122</v>
       </c>
@@ -6600,7 +6606,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="27">
         <v>123</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="27">
         <v>124</v>
       </c>
@@ -6672,7 +6678,7 @@
       </c>
       <c r="L130" s="19"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="27">
         <v>125</v>
       </c>
@@ -6706,7 +6712,7 @@
       </c>
       <c r="L131" s="20"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="27">
         <v>126</v>
       </c>
@@ -6740,7 +6746,7 @@
       </c>
       <c r="L132" s="19"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27">
         <v>127</v>
       </c>
@@ -6774,7 +6780,7 @@
       </c>
       <c r="L133" s="20"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="27">
         <v>128</v>
       </c>
@@ -6808,7 +6814,7 @@
       </c>
       <c r="L134" s="20"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="27">
         <v>129</v>
       </c>
@@ -6842,7 +6848,7 @@
       </c>
       <c r="L135" s="19"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="27">
         <v>130</v>
       </c>
@@ -6876,7 +6882,7 @@
       </c>
       <c r="L136" s="20"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="27">
         <v>131</v>
       </c>
@@ -6910,7 +6916,7 @@
       </c>
       <c r="L137" s="19"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="27">
         <v>132</v>
       </c>
@@ -6946,7 +6952,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="27">
         <v>133</v>
       </c>
@@ -6984,7 +6990,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="27">
         <v>134</v>
       </c>
@@ -7022,7 +7028,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="27">
         <v>135</v>
       </c>
@@ -7056,7 +7062,7 @@
       </c>
       <c r="L141" s="19"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="27">
         <v>136</v>
       </c>
@@ -7090,7 +7096,7 @@
       </c>
       <c r="L142" s="20"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="27">
         <v>137</v>
       </c>
@@ -7126,7 +7132,7 @@
       </c>
       <c r="L143" s="20"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="27">
         <v>138</v>
       </c>
@@ -7162,7 +7168,7 @@
       </c>
       <c r="L144" s="19"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="27">
         <v>139</v>
       </c>
@@ -7196,7 +7202,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="27">
         <v>140</v>
       </c>
@@ -7232,7 +7238,7 @@
       </c>
       <c r="L146" s="19"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="27">
         <v>141</v>
       </c>
@@ -7266,7 +7272,7 @@
       </c>
       <c r="L147" s="20"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="27">
         <v>142</v>
       </c>
@@ -7300,7 +7306,7 @@
       </c>
       <c r="L148" s="19"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="27">
         <v>143</v>
       </c>
@@ -7332,7 +7338,7 @@
       </c>
       <c r="L149" s="20"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="27">
         <v>144</v>
       </c>
@@ -7364,7 +7370,7 @@
       </c>
       <c r="L150" s="19"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="27">
         <v>145</v>
       </c>
@@ -7394,7 +7400,7 @@
       </c>
       <c r="L151" s="20"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="27">
         <v>146</v>
       </c>
@@ -7430,7 +7436,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="27">
         <v>147</v>
       </c>
@@ -7464,7 +7470,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="27">
         <v>148</v>
       </c>
@@ -7498,7 +7504,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="27">
         <v>149</v>
       </c>
@@ -7534,7 +7540,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="27">
         <v>150</v>
       </c>
@@ -7568,7 +7574,7 @@
       </c>
       <c r="L156" s="19"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="27">
         <v>151</v>
       </c>
@@ -7602,7 +7608,7 @@
       </c>
       <c r="L157" s="20"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="27">
         <v>152</v>
       </c>
@@ -7632,7 +7638,7 @@
       </c>
       <c r="L158" s="20"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="27">
         <v>153</v>
       </c>
@@ -7666,7 +7672,7 @@
       </c>
       <c r="L159" s="19"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="27">
         <v>154</v>
       </c>
@@ -7700,7 +7706,7 @@
       </c>
       <c r="L160" s="20"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="27">
         <v>155</v>
       </c>
@@ -7732,7 +7738,7 @@
       </c>
       <c r="L161" s="19"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="27">
         <v>156</v>
       </c>
@@ -7768,7 +7774,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="27">
         <v>157</v>
       </c>
@@ -7798,7 +7804,7 @@
       </c>
       <c r="L163" s="19"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="27">
         <v>158</v>
       </c>
@@ -7834,7 +7840,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="27">
         <v>159</v>
       </c>
@@ -7870,7 +7876,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="27">
         <v>160</v>
       </c>
@@ -7904,7 +7910,7 @@
       </c>
       <c r="L166" s="19"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="27">
         <v>161</v>
       </c>
@@ -7938,7 +7944,7 @@
       </c>
       <c r="L167" s="19"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="27">
         <v>162</v>
       </c>
@@ -7972,7 +7978,7 @@
       </c>
       <c r="L168" s="19"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="27">
         <v>163</v>
       </c>
@@ -8022,7 +8028,7 @@
       <c r="J170" s="25"/>
       <c r="K170" s="26">
         <f>SUBTOTAL(103,'BM POPULATION'!$K$8:$K$169)</f>
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="L170" s="3"/>
     </row>
